--- a/Employee_Reports_wi52/Harsha Shetty Q0603.xlsx
+++ b/Employee_Reports_wi52/Harsha Shetty Q0603.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1341,11 +1341,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1440,11 +1440,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1489,11 +1489,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1526,11 +1526,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1575,11 +1575,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1624,11 +1624,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1722,11 +1722,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1771,11 +1771,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1820,11 +1820,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1869,11 +1869,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1918,11 +1918,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1955,11 +1955,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2004,11 +2004,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2041,11 +2041,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2090,11 +2090,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7776</v>
+        <v>7768</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7952</v>
+        <v>7944</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7952</v>
+        <v>7944</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7953</v>
+        <v>7945</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
